--- a/output/full_scan/batch_seq8_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6996</v>
+        <v>8021</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>846.4519080312209</v>
+        <v>878.7526113448456</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>197.5</v>
+        <v>567</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.30789488781377</v>
+        <v>62.97406721299107</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.4679204160828</v>
+        <v>23.66458833705638</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.200752040728427</v>
+        <v>0.2351535170038123</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3955486214860455</v>
+        <v>5.224621939802077</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6907</v>
+        <v>6996</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>811.401708317823</v>
+        <v>846.4519080312209</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>160</v>
+        <v>197.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.64911374879631</v>
+        <v>56.30789488781377</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.13980950097201</v>
+        <v>25.4679204160828</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.233431955750699</v>
+        <v>1.200752040728427</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.783153880547041</v>
+        <v>-0.3955486214860455</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7712</v>
+        <v>6907</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>766.8188770497819</v>
+        <v>811.401708317823</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.06963657523373</v>
+        <v>63.64911374879631</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.87200450070116</v>
+        <v>27.13980950097201</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.004368014983458</v>
+        <v>1.233431955750699</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.679604316175321</v>
+        <v>0.783153880547041</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6909</v>
+        <v>7712</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>744.0833758755684</v>
+        <v>766.8188770497819</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>61.4</v>
+        <v>200</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>68.70795119742891</v>
+        <v>71.06963657523373</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.20025245797573</v>
+        <v>25.87200450070116</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.696471837804169</v>
+        <v>3.004368014983458</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.480853934189597</v>
+        <v>4.679604316175321</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8043</v>
+        <v>6909</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>737.0011327118824</v>
+        <v>744.0833758755684</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>202</v>
+        <v>61.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.54073079106291</v>
+        <v>68.70795119742891</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>44.33541658960407</v>
+        <v>21.20025245797573</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4632991491011616</v>
+        <v>2.696471837804169</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.4834236728531</v>
+        <v>1.480853934189597</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7799</v>
+        <v>8043</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>713.6737043465799</v>
+        <v>737.0011327118824</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>424.5</v>
+        <v>202</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>70.55387619859314</v>
+        <v>64.54073079106291</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.48904963752839</v>
+        <v>44.33541658960407</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.967370434657998</v>
+        <v>0.4632991491011616</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>7.56174668840095</v>
+        <v>1.4834236728531</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8046</v>
+        <v>7799</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>709.6438475897928</v>
+        <v>713.6737043465799</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>909</v>
+        <v>424.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.39363898911886</v>
+        <v>70.55387619859314</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.36615638795944</v>
+        <v>31.48904963752839</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.922535778467497</v>
+        <v>1.967370434657998</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5410461007258505</v>
+        <v>7.56174668840095</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6916</v>
+        <v>8046</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>679.550450073602</v>
+        <v>709.6438475897928</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21.1</v>
+        <v>909</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.32217315790904</v>
+        <v>55.39363898911886</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.63013432438574</v>
+        <v>14.36615638795944</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5550450073601962</v>
+        <v>1.922535778467497</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.209545330421822</v>
+        <v>0.5410461007258505</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6949</v>
+        <v>6890</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>678.2576586009192</v>
+        <v>699.5300761609086</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>833</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.20559788103061</v>
+        <v>59.41269477843976</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.92215927191345</v>
+        <v>31.03205499033814</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8958478438728082</v>
+        <v>0.1863710650250694</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>22.03399065923006</v>
+        <v>-2.560653023717325</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7788</v>
+        <v>6916</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>667.4063248727651</v>
+        <v>679.550450073602</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>278.5</v>
+        <v>21.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>68.05916412849564</v>
+        <v>57.32217315790904</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>44.02323846681626</v>
+        <v>33.63013432438574</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.691149345586317</v>
+        <v>0.5550450073601962</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.828436108780323</v>
+        <v>0.209545330421822</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7610</v>
+        <v>6949</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>665.4752709703807</v>
+        <v>678.2576586009192</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2415</v>
+        <v>833</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>77.66088087867131</v>
+        <v>62.20559788103061</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>56.39908368840333</v>
+        <v>29.92215927191345</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.969234242889041</v>
+        <v>0.8958478438728082</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>53.39372422429244</v>
+        <v>22.03399065923006</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8032</v>
+        <v>7788</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>660.5804358963178</v>
+        <v>667.4063248727651</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>46.1</v>
+        <v>278.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.33112865755236</v>
+        <v>68.05916412849564</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.79749318695106</v>
+        <v>44.02323846681626</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4901820421385582</v>
+        <v>0.691149345586317</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0338931716080634</v>
+        <v>3.828436108780323</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7556</v>
+        <v>7610</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>644.9079397142164</v>
+        <v>665.4752709703807</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>282</v>
+        <v>2415</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>52.94612668876409</v>
+        <v>77.66088087867131</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.45228662890599</v>
+        <v>56.39908368840333</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.713863322456969</v>
+        <v>1.969234242889041</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0138725224118823</v>
+        <v>53.39372422429244</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7795</v>
+        <v>8032</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>637.5327803958654</v>
+        <v>660.5804358963178</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>431.5</v>
+        <v>46.1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.5611888303892</v>
+        <v>57.33112865755236</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.59215321078066</v>
+        <v>28.79749318695106</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.125382310019509</v>
+        <v>0.4901820421385582</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>6.40135107897653</v>
+        <v>0.0338931716080634</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7715</v>
+        <v>7556</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>634.2796258690393</v>
+        <v>644.9079397142164</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>35.8</v>
+        <v>282</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>77.2052395388996</v>
+        <v>52.94612668876409</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.04639962016424</v>
+        <v>14.45228662890599</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.027962586903921</v>
+        <v>0.713863322456969</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.8418037064921799</v>
+        <v>0.0138725224118823</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7753</v>
+        <v>7795</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>608.2216756010567</v>
+        <v>637.5327803958654</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.75</v>
+        <v>431.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.39799525098937</v>
+        <v>59.5611888303892</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.79366025000355</v>
+        <v>15.59215321078066</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6.857273643790124</v>
+        <v>2.125382310019509</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.009020086309049</v>
+        <v>6.40135107897653</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6894</v>
+        <v>7715</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>606.9384912331565</v>
+        <v>634.2796258690393</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>377.5</v>
+        <v>35.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.94136667394029</v>
+        <v>77.2052395388996</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.5840250773232</v>
+        <v>34.04639962016424</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7844412841538322</v>
+        <v>3.027962586903921</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.8658599958402386</v>
+        <v>0.8418037064921799</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6962</v>
+        <v>7753</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>602.982191649049</v>
+        <v>608.2216756010567</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>39</v>
+        <v>43.75</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.32834716511589</v>
+        <v>59.39799525098937</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.70521779243511</v>
+        <v>17.79366025000355</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.172106738948961</v>
+        <v>6.857273643790124</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3380964455492104</v>
+        <v>0.009020086309049</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6957</v>
+        <v>6894</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>600.2471825462592</v>
+        <v>606.9384912331565</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>187</v>
+        <v>377.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.51098363195235</v>
+        <v>53.94136667394029</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.04718262194713</v>
+        <v>23.5840250773232</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2704218402409923</v>
+        <v>0.7844412841538322</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.5347178918310096</v>
+        <v>0.8658599958402386</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7827</v>
+        <v>6962</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>594.8866534259499</v>
+        <v>602.982191649049</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.11139727360312</v>
+        <v>57.32834716511589</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.21171365385534</v>
+        <v>16.70521779243511</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6267340466864252</v>
+        <v>1.172106738948961</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0548886082310167</v>
+        <v>0.3380964455492104</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6870</v>
+        <v>6957</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>591.8964962746046</v>
+        <v>600.2471825462592</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>262.5</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.88303367876975</v>
+        <v>59.51098363195235</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>28.80769987852472</v>
+        <v>27.04718262194713</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4955383435187016</v>
+        <v>0.2704218402409923</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-6.033176345814319</v>
+        <v>-0.5347178918310096</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6901</v>
+        <v>7827</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>588.096255926146</v>
+        <v>594.8866534259499</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>16.95</v>
+        <v>161</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>67.01866283241979</v>
+        <v>57.11139727360312</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>38.3009783459444</v>
+        <v>22.21171365385534</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7837108783312774</v>
+        <v>0.6267340466864252</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.218521788397247</v>
+        <v>-0.0548886082310167</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8028</v>
+        <v>6870</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>581.447614046666</v>
+        <v>591.8964962746046</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>310</v>
+        <v>262.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.99393633041125</v>
+        <v>49.88303367876975</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>39.94527333024367</v>
+        <v>28.80769987852472</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7904895318454724</v>
+        <v>0.4955383435187016</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-4.620623667959533</v>
+        <v>-6.033176345814319</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6944</v>
+        <v>6901</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>577.9681485390425</v>
+        <v>588.096255926146</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1060</v>
+        <v>16.95</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>68.19452589548648</v>
+        <v>67.01866283241979</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.99932671764638</v>
+        <v>38.3009783459444</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7789729603803098</v>
+        <v>0.7837108783312774</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>13.31361913698993</v>
+        <v>0.218521788397247</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8044</v>
+        <v>8028</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>563.4484114182055</v>
+        <v>581.447614046666</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.65</v>
+        <v>310</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.45741482672834</v>
+        <v>52.99393633041125</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.2849873645503</v>
+        <v>39.94527333024367</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4436308756913339</v>
+        <v>0.7904895318454724</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.2099703258275556</v>
+        <v>-4.620623667959533</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6902</v>
+        <v>6944</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>554.1846830149278</v>
+        <v>577.9681485390425</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>138</v>
+        <v>1060</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>57.19954816108441</v>
+        <v>68.19452589548648</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.59612986500923</v>
+        <v>19.99932671764638</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6511508553302792</v>
+        <v>0.7789729603803098</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-2.166191946419307</v>
+        <v>13.31361913698993</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7734</v>
+        <v>8044</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>539.800393267008</v>
+        <v>563.4484114182055</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>3390</v>
+        <v>29.65</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.97043834293486</v>
+        <v>53.45741482672834</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.93445033836064</v>
+        <v>24.2849873645503</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4931487522638342</v>
+        <v>0.4436308756913339</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>29.27862496943636</v>
+        <v>-0.2099703258275556</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6859</v>
+        <v>6902</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>536.8121557251402</v>
+        <v>554.1846830149278</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.25293021408339</v>
+        <v>57.19954816108441</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29.18253275318658</v>
+        <v>28.59612986500923</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8914014770104827</v>
+        <v>0.6511508553302792</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4068213240860139</v>
+        <v>-2.166191946419307</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7769</v>
+        <v>7734</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>521.9708577759692</v>
+        <v>539.800393267008</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6810</v>
+        <v>3390</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.00043414292588</v>
+        <v>51.97043834293486</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.56548144747025</v>
+        <v>22.93445033836064</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7044342559665737</v>
+        <v>0.4931487522638342</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-126.1970910329629</v>
+        <v>29.27862496943636</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7631</v>
+        <v>6859</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>511.6067827930135</v>
+        <v>536.8121557251402</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>137.5</v>
+        <v>130</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.69313329307521</v>
+        <v>53.25293021408339</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.99058558165039</v>
+        <v>29.18253275318658</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.141717934597029</v>
+        <v>0.8914014770104827</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.648535106885883</v>
+        <v>0.4068213240860139</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6928</v>
+        <v>7769</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>501.8738335223979</v>
+        <v>521.9708577759692</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>49.2</v>
+        <v>6810</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.1471824693401</v>
+        <v>47.00043414292588</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.40684525873264</v>
+        <v>22.56548144747025</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.011638332486196</v>
+        <v>0.7044342559665737</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4998439237105921</v>
+        <v>-126.1970910329629</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6862</v>
+        <v>7631</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>489.4810205302214</v>
+        <v>511.6067827930135</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>203.5</v>
+        <v>137.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.51991980843403</v>
+        <v>54.69313329307521</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.14613327263847</v>
+        <v>11.99058558165039</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.848102053022136</v>
+        <v>1.141717934597029</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.356374032530837</v>
+        <v>2.648535106885883</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7402</v>
+        <v>6928</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>485.6921934280942</v>
+        <v>501.8738335223979</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>103</v>
+        <v>49.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.46334493457642</v>
+        <v>59.1471824693401</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.47097677334532</v>
+        <v>21.40684525873264</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.674648141193949</v>
+        <v>1.011638332486196</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.450059123455073</v>
+        <v>0.4998439237105921</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7722</v>
+        <v>6862</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>484.7679627630494</v>
+        <v>489.4810205302214</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>306</v>
+        <v>203.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.47606276494113</v>
+        <v>52.51991980843403</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>35.60864650269288</v>
+        <v>25.14613327263847</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5092886283329989</v>
+        <v>0.848102053022136</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4930536015098958</v>
+        <v>1.356374032530837</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7750</v>
+        <v>7402</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>484.2556689358536</v>
+        <v>485.6921934280942</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2165</v>
+        <v>103</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.33070934809402</v>
+        <v>56.46334493457642</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.04083371026343</v>
+        <v>20.47097677334532</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9340618211353198</v>
+        <v>3.674648141193949</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-6.122665174387041</v>
+        <v>1.450059123455073</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7749</v>
+        <v>7722</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>478.0427255002033</v>
+        <v>484.7679627630494</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>477</v>
+        <v>306</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.22356017802628</v>
+        <v>50.47606276494113</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.50839608787883</v>
+        <v>35.60864650269288</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3517584814480659</v>
+        <v>0.5092886283329989</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-3.451554680362857</v>
+        <v>0.4930536015098958</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6919</v>
+        <v>7750</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>473.0972356639342</v>
+        <v>484.2556689358536</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>108</v>
+        <v>2165</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.17007294771037</v>
+        <v>45.33070934809402</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.17705954851919</v>
+        <v>20.04083371026343</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.934740424771872</v>
+        <v>0.9340618211353198</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.488694963875248</v>
+        <v>-6.122665174387041</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6965</v>
+        <v>7749</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>467.0920970832746</v>
+        <v>478.0427255002033</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>477</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.45741452168003</v>
+        <v>47.22356017802628</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.69263635366165</v>
+        <v>23.50839608787883</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.393502476622021</v>
+        <v>0.3517584814480659</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0518094424516737</v>
+        <v>-3.451554680362857</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8039</v>
+        <v>6919</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>464.8515190728088</v>
+        <v>473.0972356639342</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>145.5</v>
+        <v>108</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.50214126185991</v>
+        <v>57.17007294771037</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.41499126986798</v>
+        <v>19.17705954851919</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5039449821312487</v>
+        <v>1.934740424771872</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3313143995788108</v>
+        <v>2.488694963875248</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6971</v>
+        <v>6965</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>453.3009305998629</v>
+        <v>467.0920970832746</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>28.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>58.30976089983504</v>
+        <v>48.45741452168003</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.09794590645961</v>
+        <v>23.69263635366165</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.486963579182307</v>
+        <v>1.393502476622021</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2240852138310297</v>
+        <v>0.0518094424516737</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8033</v>
+        <v>8039</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>450.2782095018508</v>
+        <v>464.8515190728088</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>141</v>
+        <v>145.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.66441509514306</v>
+        <v>51.50214126185991</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.0503036844366</v>
+        <v>21.41499126986798</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.610204771900784</v>
+        <v>0.5039449821312487</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.356757750313756</v>
+        <v>0.3313143995788108</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7747</v>
+        <v>6971</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>443.7808144940298</v>
+        <v>453.3009305998629</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>126</v>
+        <v>28.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.8073119965563</v>
+        <v>58.30976089983504</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6.319198837462527</v>
+        <v>21.09794590645961</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.500715446910843</v>
+        <v>0.486963579182307</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.2799580361935918</v>
+        <v>0.2240852138310297</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7704</v>
+        <v>8033</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>442.7606145648099</v>
+        <v>450.2782095018508</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>63.7</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>57.35948118685805</v>
+        <v>56.66441509514306</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.68895610604551</v>
+        <v>10.0503036844366</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.782474175995678</v>
+        <v>2.610204771900784</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0121546916097141</v>
+        <v>1.356757750313756</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6861</v>
+        <v>7747</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>441.4917240583483</v>
+        <v>443.7808144940298</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>358</v>
+        <v>126</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.77216339304736</v>
+        <v>50.8073119965563</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.84697415750328</v>
+        <v>6.319198837462527</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7024632951146865</v>
+        <v>1.500715446910843</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.394568876988572</v>
+        <v>-0.2799580361935918</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7721</v>
+        <v>7704</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>437.6961596582789</v>
+        <v>442.7606145648099</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>73</v>
+        <v>63.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.70268802639004</v>
+        <v>57.35948118685805</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.04913322974626</v>
+        <v>13.68895610604551</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9141247940214212</v>
+        <v>1.782474175995678</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.5350572153940909</v>
+        <v>-0.0121546916097141</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6922</v>
+        <v>6861</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>432.069673957493</v>
+        <v>441.4917240583483</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>180</v>
+        <v>358</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.795170070319</v>
+        <v>50.77216339304736</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.41671278194237</v>
+        <v>25.84697415750328</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3329058974201626</v>
+        <v>0.7024632951146865</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.981359554934873</v>
+        <v>-1.394568876988572</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6887</v>
+        <v>7721</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>426.2364550028225</v>
+        <v>437.6961596582789</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.12285078106922</v>
+        <v>44.70268802639004</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>6.245757330660361</v>
+        <v>16.04913322974626</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.980662614387816</v>
+        <v>0.9141247940214212</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3383032852983982</v>
+        <v>-0.5350572153940909</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7792</v>
+        <v>6924</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>423.4521474745658</v>
+        <v>435.429480669023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>283</v>
+        <v>119.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.71156249263301</v>
+        <v>42.1205137599675</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.12595597908563</v>
+        <v>31.99216189522832</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8146125871356948</v>
+        <v>0.1212943674061022</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>3.355353819989612</v>
+        <v>-5.347849773914057</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6997</v>
+        <v>6922</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>416.8937455086792</v>
+        <v>432.069673957493</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>180</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.84201835977056</v>
+        <v>44.795170070319</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.712851090007337</v>
+        <v>19.41671278194237</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2499707546530886</v>
+        <v>0.3329058974201626</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.8256333606093231</v>
+        <v>-1.981359554934873</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6983</v>
+        <v>6887</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>408.90121552019</v>
+        <v>426.2364550028225</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>381</v>
+        <v>37</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.80608201304513</v>
+        <v>54.12285078106922</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.26201679569353</v>
+        <v>6.245757330660361</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8781915292436479</v>
+        <v>1.980662614387816</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>4.469579559137019</v>
+        <v>0.3383032852983982</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6951</v>
+        <v>7792</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>408.7087148174514</v>
+        <v>423.4521474745658</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>77.7</v>
+        <v>283</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>36.7741380115889</v>
+        <v>51.71156249263301</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.66231887467358</v>
+        <v>20.12595597908563</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8628186506454721</v>
+        <v>0.8146125871356948</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.482349329560485</v>
+        <v>3.355353819989612</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7728</v>
+        <v>6997</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>403.0607217379679</v>
+        <v>416.8937455086792</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>715</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.27478885350898</v>
+        <v>51.84201835977056</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.35985058849589</v>
+        <v>8.712851090007337</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2919676931122593</v>
+        <v>0.2499707546530886</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.6469522613199361</v>
+        <v>0.8256333606093231</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7786</v>
+        <v>6983</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>399.4327098691248</v>
+        <v>408.90121552019</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>126.5</v>
+        <v>381</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.56033112730417</v>
+        <v>51.80608201304513</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.3019238648667</v>
+        <v>14.26201679569353</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4690312431532978</v>
+        <v>0.8781915292436479</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.101915617988101</v>
+        <v>4.469579559137019</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6906</v>
+        <v>6951</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>384.5802122588451</v>
+        <v>408.7087148174514</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>88</v>
+        <v>77.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.61134921060811</v>
+        <v>36.7741380115889</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>26.49091618545692</v>
+        <v>25.66231887467358</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4162605353150401</v>
+        <v>0.8628186506454721</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.094908707648927</v>
+        <v>-0.482349329560485</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7714</v>
+        <v>7728</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>375.6336957515318</v>
+        <v>403.0607217379679</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>129.5</v>
+        <v>715</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.24056825947224</v>
+        <v>47.27478885350898</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.08897159955938</v>
+        <v>11.35985058849589</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2812254931217651</v>
+        <v>0.2919676931122593</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0656790902083859</v>
+        <v>-0.6469522613199361</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7768</v>
+        <v>7786</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>366.0517061562181</v>
+        <v>399.4327098691248</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>360.5</v>
+        <v>126.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.19707048410588</v>
+        <v>51.56033112730417</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.73985381225555</v>
+        <v>21.3019238648667</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7772778547311792</v>
+        <v>0.4690312431532978</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.839530993451687</v>
+        <v>1.101915617988101</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7839</v>
+        <v>6906</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>364.302722972685</v>
+        <v>384.5802122588451</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.05975568771642</v>
+        <v>48.61134921060811</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6.684772237176746</v>
+        <v>26.49091618545692</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.330272297268505</v>
+        <v>0.4162605353150401</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.090208158163065</v>
+        <v>-2.094908707648927</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7822</v>
+        <v>7714</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>359.3623012407506</v>
+        <v>375.6336957515318</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1200</v>
+        <v>129.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.27515746899637</v>
+        <v>51.24056825947224</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.21887348471154</v>
+        <v>23.08897159955938</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.090719256876131</v>
+        <v>0.2812254931217651</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>28.57377088343023</v>
+        <v>0.0656790902083859</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6877</v>
+        <v>7768</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>349.5514728059325</v>
+        <v>366.0517061562181</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>127</v>
+        <v>360.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.14920984619228</v>
+        <v>40.19707048410588</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.00436739766188</v>
+        <v>16.73985381225555</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3240989174760682</v>
+        <v>0.7772778547311792</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.784920437541363</v>
+        <v>-2.839530993451687</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7760</v>
+        <v>7839</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>349.4572523456977</v>
+        <v>364.302722972685</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>32.7</v>
+        <v>43</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46.75630035612453</v>
+        <v>42.05975568771642</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46.1443881888267</v>
+        <v>6.684772237176746</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.011207492162544</v>
+        <v>1.330272297268505</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.303635721859244</v>
+        <v>-2.090208158163065</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7805</v>
+        <v>7822</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>347.6511018402334</v>
+        <v>359.3623012407506</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>678</v>
+        <v>1200</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>35.63244746882586</v>
+        <v>54.27515746899637</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>26.7366443186708</v>
+        <v>17.21887348471154</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7483519291627418</v>
+        <v>1.090719256876131</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-8.740597477384883</v>
+        <v>28.57377088343023</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7772</v>
+        <v>6877</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>340.1294780696025</v>
+        <v>349.5514728059325</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.67423205421835</v>
+        <v>34.14920984619228</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.203611071635001</v>
+        <v>22.00436739766188</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4245096535505871</v>
+        <v>0.3240989174760682</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.4839357036050984</v>
+        <v>-1.784920437541363</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6933</v>
+        <v>7760</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>335.7059670329188</v>
+        <v>349.4572523456977</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>152.5</v>
+        <v>32.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.01527108678904</v>
+        <v>46.75630035612453</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.92364504974856</v>
+        <v>46.1443881888267</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4576024383537254</v>
+        <v>1.011207492162544</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.8477344885725797</v>
+        <v>0.303635721859244</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6899</v>
+        <v>7805</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>333.3204522194035</v>
+        <v>347.6511018402334</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>59</v>
+        <v>678</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.82417047374615</v>
+        <v>35.63244746882586</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.2896101344054</v>
+        <v>26.7366443186708</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2988669414679604</v>
+        <v>0.7483519291627418</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.6272655450776023</v>
+        <v>-8.740597477384883</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6895</v>
+        <v>7772</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>325.5265376816398</v>
+        <v>340.1294780696025</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.59456899378898</v>
+        <v>42.67423205421835</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.41396862470454</v>
+        <v>9.203611071635001</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.144045160950634</v>
+        <v>0.4245096535505871</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2064781654447484</v>
+        <v>-0.4839357036050984</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6865</v>
+        <v>6933</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>323.8344858319792</v>
+        <v>335.7059670329188</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.8</v>
+        <v>152.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.48041585347485</v>
+        <v>43.01527108678904</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.07219009260236</v>
+        <v>17.92364504974856</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.831712961211588</v>
+        <v>0.4576024383537254</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.6463804560730075</v>
+        <v>-0.8477344885725797</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6855</v>
+        <v>6899</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>318.6022029429706</v>
+        <v>333.3204522194035</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.51869724397727</v>
+        <v>43.82417047374615</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.63634601221199</v>
+        <v>19.2896101344054</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3288629448632422</v>
+        <v>0.2988669414679604</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-3.849441322346269</v>
+        <v>-0.6272655450776023</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7780</v>
+        <v>6895</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>318.5307662890571</v>
+        <v>325.5265376816398</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18.2</v>
+        <v>155</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.8507798198803</v>
+        <v>44.59456899378898</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.32382208704134</v>
+        <v>20.41396862470454</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8171854884342763</v>
+        <v>1.144045160950634</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1167066596664139</v>
+        <v>0.2064781654447484</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7736</v>
+        <v>6865</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>315.151587424634</v>
+        <v>323.8344858319792</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.28680392072309</v>
+        <v>49.48041585347485</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.97139351736754</v>
+        <v>20.07219009260236</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5059354554443779</v>
+        <v>0.831712961211588</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.182604626808708</v>
+        <v>0.6463804560730075</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6918</v>
+        <v>6855</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>314.0672965846733</v>
+        <v>318.6022029429706</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>73.2</v>
+        <v>118</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.12053879170895</v>
+        <v>51.51869724397727</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6.438174237642949</v>
+        <v>16.63634601221199</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4121698294260922</v>
+        <v>0.3288629448632422</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0718827455953258</v>
+        <v>-3.849441322346269</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6903</v>
+        <v>7780</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>311.9557139674922</v>
+        <v>318.5307662890571</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>381</v>
+        <v>18.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.50950099962427</v>
+        <v>43.8507798198803</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.73583504510684</v>
+        <v>18.32382208704134</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4885112552888046</v>
+        <v>0.8171854884342763</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.347677796044892</v>
+        <v>0.1167066596664139</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7751</v>
+        <v>7736</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>310.7110780336452</v>
+        <v>315.151587424634</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1475</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.29846766883514</v>
+        <v>47.28680392072309</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.67056448722409</v>
+        <v>15.97139351736754</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6319550966217808</v>
+        <v>0.5059354554443779</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>12.76604402954769</v>
+        <v>0.182604626808708</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7717</v>
+        <v>6918</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.0340304804653</v>
+        <v>314.0672965846733</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>497.5</v>
+        <v>73.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>32.50465389561982</v>
+        <v>46.12053879170895</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.89618306607867</v>
+        <v>6.438174237642949</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9713507687300074</v>
+        <v>0.4121698294260922</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-7.631259675946104</v>
+        <v>0.0718827455953258</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7711</v>
+        <v>6903</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>301.971790026177</v>
+        <v>311.9557139674922</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>39.1351718629725</v>
+        <v>46.50950099962427</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.12420681443727</v>
+        <v>13.73583504510684</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8386599540023403</v>
+        <v>0.4885112552888046</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-4.065643738749088</v>
+        <v>-1.347677796044892</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8038</v>
+        <v>7751</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>299.2853544305458</v>
+        <v>310.7110780336452</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>40.2</v>
+        <v>1475</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.41754314868267</v>
+        <v>43.29846766883514</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7.324977003303846</v>
+        <v>15.67056448722409</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.815680244887665</v>
+        <v>0.6319550966217808</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0128459928464797</v>
+        <v>12.76604402954769</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6923</v>
+        <v>7717</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>296.4557243403337</v>
+        <v>307.0340304804653</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>78.2</v>
+        <v>497.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.97622222943126</v>
+        <v>32.50465389561982</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.44652086838189</v>
+        <v>12.89618306607867</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7628615162957172</v>
+        <v>0.9713507687300074</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.09305571819513631</v>
+        <v>-7.631259675946104</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7744</v>
+        <v>7711</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>296.3518129701966</v>
+        <v>301.971790026177</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>454</v>
+        <v>340</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.54179404014583</v>
+        <v>39.1351718629725</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.63486665920495</v>
+        <v>15.12420681443727</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6635805325788395</v>
+        <v>0.8386599540023403</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.8168258455596629</v>
+        <v>-4.065643738749088</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7820</v>
+        <v>8038</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>290.9887864523873</v>
+        <v>299.2853544305458</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>115</v>
+        <v>40.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33.6263097858247</v>
+        <v>44.41754314868267</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>30.19000743852852</v>
+        <v>7.324977003303846</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.972660886707714</v>
+        <v>0.815680244887665</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.9503389537457484</v>
+        <v>-0.0128459928464797</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6910</v>
+        <v>6923</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>290.4616781738188</v>
+        <v>296.4557243403337</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>27.85</v>
+        <v>78.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.53825205138119</v>
+        <v>46.97622222943126</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.75833896589578</v>
+        <v>12.44652086838189</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2692788039881739</v>
+        <v>0.7628615162957172</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0751438607288555</v>
+        <v>0.09305571819513631</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6967</v>
+        <v>7744</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.6064662723102</v>
+        <v>296.3518129701966</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>70.8</v>
+        <v>454</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.4266574516004</v>
+        <v>39.54179404014583</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.654585627171532</v>
+        <v>12.63486665920495</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.173798388720383</v>
+        <v>0.6635805325788395</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2740346413101499</v>
+        <v>-0.8168258455596629</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6913</v>
+        <v>7820</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>281.4368386390648</v>
+        <v>290.9887864523873</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.57278637051117</v>
+        <v>33.6263097858247</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.0622089949202</v>
+        <v>30.19000743852852</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4875016673466108</v>
+        <v>0.972660886707714</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.162270244593728</v>
+        <v>0.9503389537457484</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6925</v>
+        <v>6910</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>281.3060293709275</v>
+        <v>290.4616781738188</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>62.6</v>
+        <v>27.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.69996169650828</v>
+        <v>43.53825205138119</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.70050218162057</v>
+        <v>12.75833896589578</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1676273226201875</v>
+        <v>0.2692788039881739</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.6665103182598278</v>
+        <v>-0.0751438607288555</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6914</v>
+        <v>6967</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>279.8924814374572</v>
+        <v>286.6064662723102</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>143</v>
+        <v>70.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.24233481600045</v>
+        <v>47.4266574516004</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.47110591136212</v>
+        <v>9.654585627171532</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3192936449469509</v>
+        <v>1.173798388720383</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.3797780941498968</v>
+        <v>0.2740346413101499</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7705</v>
+        <v>6913</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>279.1388207808004</v>
+        <v>281.4368386390648</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>31.85</v>
+        <v>123</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.28749460171969</v>
+        <v>41.57278637051117</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.51034674162333</v>
+        <v>16.0622089949202</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3472330329173617</v>
+        <v>0.4875016673466108</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1286460537936609</v>
+        <v>-1.162270244593728</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6937</v>
+        <v>6925</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>278.6915878903224</v>
+        <v>281.3060293709275</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>277</v>
+        <v>62.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.00601573047118</v>
+        <v>44.69996169650828</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.76825288024627</v>
+        <v>19.70050218162057</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5194991726709235</v>
+        <v>0.1676273226201875</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.4748353625276289</v>
+        <v>-0.6665103182598278</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8047</v>
+        <v>6914</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>277.302970581288</v>
+        <v>279.8924814374572</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>47.8</v>
+        <v>143</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>47.89123522688092</v>
+        <v>51.24233481600045</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6.61756998426641</v>
+        <v>13.47110591136212</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1003241751943108</v>
+        <v>0.3192936449469509</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0568322129332342</v>
+        <v>0.3797780941498968</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6994</v>
+        <v>7705</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>274.3503796934199</v>
+        <v>279.1388207808004</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>51.3</v>
+        <v>31.85</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>30.93863390431264</v>
+        <v>51.28749460171969</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.54771395136661</v>
+        <v>16.51034674162333</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.226575995089944</v>
+        <v>0.3472330329173617</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.676874314137174</v>
+        <v>0.1286460537936609</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7842</v>
+        <v>6937</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>263.7418745789875</v>
+        <v>278.6915878903224</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>277</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>32.38787627193011</v>
+        <v>45.00601573047118</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>26.55403732284784</v>
+        <v>12.76825288024627</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4627853019242133</v>
+        <v>0.5194991726709235</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.519840414028355</v>
+        <v>-0.4748353625276289</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7703</v>
+        <v>8047</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>263.4332873046293</v>
+        <v>277.302970581288</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>203</v>
+        <v>47.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.43284384306064</v>
+        <v>47.89123522688092</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.10277485507888</v>
+        <v>6.61756998426641</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.822801776498347</v>
+        <v>0.1003241751943108</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.215931960116439</v>
+        <v>0.0568322129332342</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6952</v>
+        <v>6994</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.9597683142277</v>
+        <v>274.3503796934199</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>35.85</v>
+        <v>51.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>37.91174064161</v>
+        <v>30.93863390431264</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.82022077726655</v>
+        <v>19.54771395136661</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8297540632186148</v>
+        <v>1.226575995089944</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0518900040909985</v>
+        <v>-0.676874314137174</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6931</v>
+        <v>7842</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.4161362448886</v>
+        <v>263.7418745789875</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>40.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>35.10512186697804</v>
+        <v>32.38787627193011</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>22.87757018916969</v>
+        <v>26.55403732284784</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9310533255802828</v>
+        <v>0.4627853019242133</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.204272900518085</v>
+        <v>0.519840414028355</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6955</v>
+        <v>7703</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.5169035004229</v>
+        <v>263.4332873046293</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>126.5</v>
+        <v>203</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.08605730556172</v>
+        <v>47.43284384306064</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5.922786073219664</v>
+        <v>12.10277485507888</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.238082544063225</v>
+        <v>0.822801776498347</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.321603181925176</v>
+        <v>1.215931960116439</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6936</v>
+        <v>6952</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>248.4055501876153</v>
+        <v>252.9597683142277</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>32.6</v>
+        <v>35.85</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.34265756505848</v>
+        <v>37.91174064161</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.02645693097096</v>
+        <v>20.82022077726655</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6074052592794164</v>
+        <v>0.8297540632186148</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0437978854298933</v>
+        <v>0.0518900040909985</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6863</v>
+        <v>6931</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>247.5025604167544</v>
+        <v>251.4161362448886</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>93.5</v>
+        <v>40.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.90732364853181</v>
+        <v>35.10512186697804</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>22.77598689612634</v>
+        <v>22.87757018916969</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9177096365706572</v>
+        <v>0.9310533255802828</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.049697995436213</v>
+        <v>0.204272900518085</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7738</v>
+        <v>6955</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>244.6967712257732</v>
+        <v>249.5169035004229</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>169.5</v>
+        <v>126.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.60314884707996</v>
+        <v>44.08605730556172</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24.35944683719621</v>
+        <v>5.922786073219664</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5851647111185649</v>
+        <v>1.238082544063225</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.595955931132885</v>
+        <v>-1.321603181925176</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6921</v>
+        <v>6936</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>243.2280794607738</v>
+        <v>248.4055501876153</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>70</v>
+        <v>32.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.17882322842236</v>
+        <v>37.34265756505848</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>26.71281750198446</v>
+        <v>11.02645693097096</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.430716838069185</v>
+        <v>0.6074052592794164</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1902567867348548</v>
+        <v>-0.0437978854298933</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7765</v>
+        <v>6863</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>240.2479035981169</v>
+        <v>247.5025604167544</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>227.5</v>
+        <v>93.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.66524734571737</v>
+        <v>34.90732364853181</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>26.69345707478684</v>
+        <v>22.77598689612634</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9247903598116824</v>
+        <v>0.9177096365706572</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-3.114810125282447</v>
+        <v>-1.049697995436213</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6854</v>
+        <v>7738</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>240.0909672681784</v>
+        <v>244.6967712257732</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>128</v>
+        <v>169.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.98477839685954</v>
+        <v>46.60314884707996</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.69341935639603</v>
+        <v>24.35944683719621</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4982474863006671</v>
+        <v>0.5851647111185649</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.5687378707237496</v>
+        <v>0.595955931132885</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7823</v>
+        <v>6921</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>240.0573565200355</v>
+        <v>243.2280794607738</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.3</v>
+        <v>70</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>26.42627499797625</v>
+        <v>38.17882322842236</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>31.20395791116651</v>
+        <v>26.71281750198446</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5907643254668153</v>
+        <v>1.430716838069185</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-1.393715224690957</v>
+        <v>0.1902567867348548</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7803</v>
+        <v>7765</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>238.3460896856574</v>
+        <v>240.2479035981169</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>22.5</v>
+        <v>227.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.69642491265894</v>
+        <v>36.66524734571737</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>20.50977792245749</v>
+        <v>26.69345707478684</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6693970703709772</v>
+        <v>0.9247903598116824</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2554812741174705</v>
+        <v>-3.114810125282447</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6969</v>
+        <v>6854</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>232.1079980017499</v>
+        <v>240.0909672681784</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>25.6</v>
+        <v>128</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>22.17193342179605</v>
+        <v>36.98477839685954</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.67697166167157</v>
+        <v>17.69341935639603</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8632164535627843</v>
+        <v>0.4982474863006671</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1213129917494967</v>
+        <v>-0.5687378707237496</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6885</v>
+        <v>7823</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>227.2989966044771</v>
+        <v>240.0573565200355</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>21.35</v>
+        <v>80.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.67096060302111</v>
+        <v>26.42627499797625</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.11067455547635</v>
+        <v>31.20395791116651</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5289356100154993</v>
+        <v>0.5907643254668153</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2811134209699795</v>
+        <v>-1.393715224690957</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7740</v>
+        <v>7803</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>220.996956894413</v>
+        <v>238.3460896856574</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>155.5</v>
+        <v>22.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.87286359211138</v>
+        <v>36.69642491265894</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.22028885451648</v>
+        <v>20.50977792245749</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3310514597106361</v>
+        <v>0.6693970703709772</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.514760242656196</v>
+        <v>0.2554812741174705</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6869</v>
+        <v>6969</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>215.8989108482114</v>
+        <v>232.1079980017499</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.08755126720683</v>
+        <v>22.17193342179605</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.04531409432174</v>
+        <v>20.67697166167157</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.768752918730768</v>
+        <v>0.8632164535627843</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.5009296802639833</v>
+        <v>-0.1213129917494967</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6908</v>
+        <v>6885</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>215.2216068748661</v>
+        <v>227.2989966044771</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>38.9</v>
+        <v>21.35</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.54444672861931</v>
+        <v>39.67096060302111</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.87647763657589</v>
+        <v>21.11067455547635</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.593231008660147</v>
+        <v>0.5289356100154993</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.07055050317722129</v>
+        <v>-0.2811134209699795</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7810</v>
+        <v>7740</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>207.7770381113316</v>
+        <v>220.996956894413</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>205</v>
+        <v>155.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.8549507578528</v>
+        <v>38.87286359211138</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.97071885932683</v>
+        <v>14.22028885451648</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5320695624019327</v>
+        <v>0.3310514597106361</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.7511032428862201</v>
+        <v>-1.514760242656196</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6934</v>
+        <v>6869</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>207.5923458506415</v>
+        <v>215.8989108482114</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>67.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.13009147074494</v>
+        <v>36.08755126720683</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>29.92280432383121</v>
+        <v>17.04531409432174</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4107984303507546</v>
+        <v>0.768752918730768</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0153282447578595</v>
+        <v>-0.5009296802639833</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7730</v>
+        <v>6908</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>203.6941010143353</v>
+        <v>215.2216068748661</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>185.5</v>
+        <v>38.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.9555458520288</v>
+        <v>46.54444672861931</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.30972646171928</v>
+        <v>10.87647763657589</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.041820069091911</v>
+        <v>1.593231008660147</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-1.430733609267038</v>
+        <v>0.07055050317722129</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7732</v>
+        <v>7810</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>201.7412671531215</v>
+        <v>207.7770381113316</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.7</v>
+        <v>205</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.68741430154793</v>
+        <v>40.8549507578528</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.48074072057244</v>
+        <v>14.97071885932683</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5297129749078693</v>
+        <v>0.5320695624019327</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1618856744832982</v>
+        <v>-0.7511032428862201</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6873</v>
+        <v>6934</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>190.5786842518771</v>
+        <v>207.5923458506415</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.54062452158468</v>
+        <v>37.13009147074494</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.06297254879478</v>
+        <v>29.92280432383121</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4877853957848211</v>
+        <v>0.4107984303507546</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.7873416909704305</v>
+        <v>0.0153282447578595</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6958</v>
+        <v>7730</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>189.1873683575082</v>
+        <v>203.6941010143353</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.25</v>
+        <v>185.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.9499076899267</v>
+        <v>48.9555458520288</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.92025381963597</v>
+        <v>16.30972646171928</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6458579275390017</v>
+        <v>1.041820069091911</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0813816709788812</v>
+        <v>-1.430733609267038</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7791</v>
+        <v>7732</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>167.4061172467397</v>
+        <v>201.7412671531215</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>61.9</v>
+        <v>35.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>34.86399749550144</v>
+        <v>51.68741430154793</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.09737996180882</v>
+        <v>15.48074072057244</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8459428510173201</v>
+        <v>0.5297129749078693</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.3873565333138968</v>
+        <v>-0.1618856744832982</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7821</v>
+        <v>6873</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>166.8865372568107</v>
+        <v>190.5786842518771</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>43.25</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.75237128606881</v>
+        <v>40.54062452158468</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.83232401477857</v>
+        <v>14.06297254879478</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5950244760449518</v>
+        <v>0.4877853957848211</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1528665064833312</v>
+        <v>-0.7873416909704305</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7818</v>
+        <v>6958</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>165.1746961273089</v>
+        <v>189.1873683575082</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>63.9</v>
+        <v>17.25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.16681050509521</v>
+        <v>48.9499076899267</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>49.56947433987869</v>
+        <v>17.92025381963597</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.330192812128201</v>
+        <v>0.6458579275390017</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.452671591307276</v>
+        <v>0.0813816709788812</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7770</v>
+        <v>7791</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>160.4434278382406</v>
+        <v>167.4061172467397</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>43.2</v>
+        <v>61.9</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.9355244178523</v>
+        <v>34.86399749550144</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>6.905250456489331</v>
+        <v>20.09737996180882</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8878966389991048</v>
+        <v>0.8459428510173201</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1638348938505544</v>
+        <v>-0.3873565333138968</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6988</v>
+        <v>7821</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>134.6288784008001</v>
+        <v>166.8865372568107</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>13.85</v>
+        <v>43.25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>33.94024280797561</v>
+        <v>38.75237128606881</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>18.07008946562749</v>
+        <v>16.83232401477857</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.737118338599362</v>
+        <v>0.5950244760449518</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.09736679244709889</v>
+        <v>0.1528665064833312</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7547</v>
+        <v>7818</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>131.9403840117225</v>
+        <v>165.1746961273089</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>58.5</v>
+        <v>63.9</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>39.50907129903079</v>
+        <v>34.16681050509521</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.33662451627898</v>
+        <v>49.56947433987869</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.2822097765665299</v>
+        <v>1.330192812128201</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1440231125228033</v>
+        <v>1.452671591307276</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6953</v>
+        <v>7770</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>128.6135105657965</v>
+        <v>160.4434278382406</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>235</v>
+        <v>43.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.51594525920108</v>
+        <v>49.9355244178523</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17.52065515874054</v>
+        <v>6.905250456489331</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3926446947375894</v>
+        <v>0.8878966389991048</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.6323115666055674</v>
+        <v>0.1638348938505544</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>8045</v>
+        <v>6988</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>122.4002506619812</v>
+        <v>134.6288784008001</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>61.5</v>
+        <v>13.85</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.12280509979368</v>
+        <v>33.94024280797561</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.95417330325656</v>
+        <v>18.07008946562749</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4268598365974212</v>
+        <v>0.737118338599362</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0328490757262045</v>
+        <v>-0.09736679244709889</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>8034</v>
+        <v>7547</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>99.66665970640402</v>
+        <v>131.9403840117225</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>23</v>
+        <v>58.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>38.47280138982749</v>
+        <v>39.50907129903079</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.17234348006493</v>
+        <v>14.33662451627898</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.884267280823485</v>
+        <v>0.2822097765665299</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0612273806632081</v>
+        <v>0.1440231125228033</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,52 +7046,211 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6953</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>家碩</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>128.6135105657965</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>46.51594525920108</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>17.52065515874054</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.3926446947375894</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.6323115666055674</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>8045</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>達運光電</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>122.4002506619812</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>40.12280509979368</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>11.95417330325656</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.4268598365974212</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0328490757262045</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>8034</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>99.66665970640402</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.47280138982749</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>17.17234348006493</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.884267280823485</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0612273806632081</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>8011</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>台通</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>98.6145242716638</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>39.66428468960834</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>15.48765871678197</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.6950447522727886</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-0.0175705432709184</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq8_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-23.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1128.503278240715</v>
+        <v>1328.503278240715</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>320.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.47117686550413</v>
+        <v>66.47117685140691</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>40.26775535284435</v>
+        <v>40.26775536211887</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.814115563112883</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2845672932695677</v>
+        <v>0.2845672940937707</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8024</v>
+        <v>8040</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>920.9662598069162</v>
+        <v>1104.003429629854</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.75</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>77.47978601315231</v>
+        <v>66.50088908450135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.11740427610466</v>
+        <v>33.92949422492171</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.582455433710689</v>
+        <v>3.298875401686582</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.10878370381009</v>
+        <v>-0.4741211045188374</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8040</v>
+        <v>8024</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>904.0034296298541</v>
+        <v>1090.966259806916</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>114</v>
+        <v>13.75</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.50088902946774</v>
+        <v>77.47978610490743</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.92949421829939</v>
+        <v>24.11740425250286</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.298875401686582</v>
+        <v>4.582455433710689</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4741211040242898</v>
+        <v>0.1087837037688786</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8021</v>
+        <v>6907</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>878.7526113448456</v>
+        <v>981.4017083178232</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>567</v>
+        <v>160</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.97406721299107</v>
+        <v>63.64911374879631</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.66458833705638</v>
+        <v>27.13980950097201</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.2351535170038123</v>
+        <v>1.233431955750699</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.224621939802077</v>
+        <v>0.783153880547041</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6996</v>
+        <v>7712</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>846.4519080312209</v>
+        <v>966.818877049782</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>197.5</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.30789488781377</v>
+        <v>71.06963658134525</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.4679204160828</v>
+        <v>25.8720046708641</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.200752040728427</v>
+        <v>3.004368014983458</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3955486214860455</v>
+        <v>4.679604316690447</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6907</v>
+        <v>6909</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>811.401708317823</v>
+        <v>944.0833758755684</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>160</v>
+        <v>61.4</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.64911374879631</v>
+        <v>68.70795114255462</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.13980950097201</v>
+        <v>21.20025257573085</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.233431955750699</v>
+        <v>2.696471837804169</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.783153880547041</v>
+        <v>1.48085393461201</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7712</v>
+        <v>7799</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>766.8188770497819</v>
+        <v>933.6737043465801</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>200</v>
+        <v>424.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71.06963657523373</v>
+        <v>70.55387626530123</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.87200450070116</v>
+        <v>31.48904954087429</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.004368014983458</v>
+        <v>1.967370434657998</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.679604316175321</v>
+        <v>7.561746686237312</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6909</v>
+        <v>8021</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>744.0833758755684</v>
+        <v>878.7526113448456</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>61.4</v>
+        <v>567</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.70795119742891</v>
+        <v>62.97406721299107</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.20025245797573</v>
+        <v>23.66458833705638</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.696471837804169</v>
+        <v>0.2351535170038123</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.480853934189597</v>
+        <v>5.224621939802077</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8043</v>
+        <v>6996</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>737.0011327118824</v>
+        <v>846.4519080312209</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>202</v>
+        <v>197.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.54073079106291</v>
+        <v>56.30789499177716</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>44.33541658960407</v>
+        <v>25.46792039906609</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4632991491011616</v>
+        <v>1.200752040728427</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.4834236728531</v>
+        <v>-0.3955486217951427</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7799</v>
+        <v>6949</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>713.6737043465799</v>
+        <v>838.2576586009192</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>424.5</v>
+        <v>833</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70.55387619859314</v>
+        <v>62.20559788716461</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.48904963752839</v>
+        <v>29.92215919700269</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.967370434657998</v>
+        <v>0.8958478438728082</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>7.56174668840095</v>
+        <v>22.03399065912708</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8046</v>
+        <v>7795</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>709.6438475897928</v>
+        <v>837.5327803958654</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>909</v>
+        <v>431.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.39363898911886</v>
+        <v>59.56118883652245</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14.36615638795944</v>
+        <v>15.59215323907077</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.922535778467497</v>
+        <v>2.125382310019509</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5410461007258505</v>
+        <v>6.401351078667454</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6890</v>
+        <v>8046</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>699.5300761609086</v>
+        <v>834.6438475897929</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>238</v>
+        <v>909</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.41269477843976</v>
+        <v>55.39363899374873</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31.03205499033814</v>
+        <v>14.36615638795944</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.1863710650250694</v>
+        <v>1.922535778467497</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-2.560653023717325</v>
+        <v>0.5410461002724887</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6916</v>
+        <v>7715</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>679.550450073602</v>
+        <v>834.2796258690393</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21.1</v>
+        <v>35.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.32217315790904</v>
+        <v>77.20523956343389</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33.63013432438574</v>
+        <v>34.04639962233929</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5550450073601962</v>
+        <v>3.027962586903921</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.209545330421822</v>
+        <v>0.8418037064818785</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6949</v>
+        <v>7788</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>678.2576586009192</v>
+        <v>807.4063248727651</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>833</v>
+        <v>278.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.20559788103061</v>
+        <v>68.0591629562831</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.92215927191345</v>
+        <v>44.02323853792471</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8958478438728082</v>
+        <v>0.691149345586317</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>22.03399065923006</v>
+        <v>3.828436108780323</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7788</v>
+        <v>6944</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>667.4063248727651</v>
+        <v>792.9681485390425</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>278.5</v>
+        <v>1060</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.05916412849564</v>
+        <v>68.19452589881315</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44.02323846681626</v>
+        <v>19.99932664038216</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.691149345586317</v>
+        <v>0.7789729603803098</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.828436108780323</v>
+        <v>13.31361913781412</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7610</v>
+        <v>7734</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>665.4752709703807</v>
+        <v>739.800393267008</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2415</v>
+        <v>3390</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>77.66088087867131</v>
+        <v>51.97043836725039</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>56.39908368840333</v>
+        <v>22.93445037457604</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.969234242889041</v>
+        <v>0.4931487522638342</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>53.39372422429244</v>
+        <v>29.27862496119408</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8032</v>
+        <v>8043</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>660.5804358963178</v>
+        <v>737.0011327118824</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>46.1</v>
+        <v>202</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.33112865755236</v>
+        <v>64.54073079645559</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>28.79749318695106</v>
+        <v>44.33541661425569</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4901820421385582</v>
+        <v>0.4632991491011616</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0338931716080634</v>
+        <v>1.483423672739757</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7556</v>
+        <v>6901</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>644.9079397142164</v>
+        <v>728.0962559261461</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>282</v>
+        <v>16.95</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.94612668876409</v>
+        <v>67.01866298633556</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.45228662890599</v>
+        <v>38.30097829163607</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.713863322456969</v>
+        <v>0.7837108783312774</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0138725224118823</v>
+        <v>0.2185217882324005</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7795</v>
+        <v>6962</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>637.5327803958654</v>
+        <v>712.9821916490488</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>431.5</v>
+        <v>39</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.5611888303892</v>
+        <v>57.32834722900618</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.59215321078066</v>
+        <v>16.70521779243511</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.125382310019509</v>
+        <v>1.172106738948961</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>6.40135107897653</v>
+        <v>0.3380964452401263</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7715</v>
+        <v>6890</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>634.2796258690393</v>
+        <v>699.5300761609086</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>35.8</v>
+        <v>238</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>77.2052395388996</v>
+        <v>59.41269477843976</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>34.04639962016424</v>
+        <v>31.03205499033814</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.027962586903921</v>
+        <v>0.1863710650250694</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>1</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.8418037064921799</v>
+        <v>-2.560653023717325</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7753</v>
+        <v>6902</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>608.2216756010567</v>
+        <v>694.1846830149278</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>43.75</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.39799525098937</v>
+        <v>57.19954821436225</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.79366025000355</v>
+        <v>28.59613000919082</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.857273643790124</v>
+        <v>0.6511508553302792</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.009020086309049</v>
+        <v>-2.166191946975653</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6894</v>
+        <v>6916</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>606.9384912331565</v>
+        <v>679.550450073602</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>377.5</v>
+        <v>21.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.94136667394029</v>
+        <v>57.32217342260223</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.5840250773232</v>
+        <v>33.63013484073559</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7844412841538322</v>
+        <v>0.5550450073601962</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.8658599958402386</v>
+        <v>0.2095453299684921</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6962</v>
+        <v>7610</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>602.982191649049</v>
+        <v>665.4752709703807</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>39</v>
+        <v>2415</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.32834716511589</v>
+        <v>77.66088087867131</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.70521779243511</v>
+        <v>56.39908368840333</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.172106738948961</v>
+        <v>1.969234242889041</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3380964455492104</v>
+        <v>53.39372422429244</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6957</v>
+        <v>8032</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>600.2471825462592</v>
+        <v>660.5804358963178</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>187</v>
+        <v>46.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.51098363195235</v>
+        <v>57.33112874823413</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.04718262194713</v>
+        <v>28.79749310484215</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2704218402409923</v>
+        <v>0.4901820421385582</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.5347178918310096</v>
+        <v>0.0338931713814003</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7827</v>
+        <v>7402</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>594.8866534259499</v>
+        <v>655.6921934280937</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.11139727360312</v>
+        <v>56.46334500446554</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.21171365385534</v>
+        <v>20.47097681066962</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6267340466864252</v>
+        <v>3.674648141193949</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0548886082310167</v>
+        <v>1.450059123042956</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6870</v>
+        <v>7556</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>591.8964962746046</v>
+        <v>644.9079397142164</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>262.5</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.88303367876975</v>
+        <v>52.94612678136091</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.80769987852472</v>
+        <v>14.45228655891774</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4955383435187016</v>
+        <v>0.713863322456969</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-6.033176345814319</v>
+        <v>0.0138725222058373</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6901</v>
+        <v>6919</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>588.096255926146</v>
+        <v>643.0972356639342</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>16.95</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>67.01866283241979</v>
+        <v>57.17007375950953</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.3009783459444</v>
+        <v>19.17705953543952</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7837108783312774</v>
+        <v>1.934740424771872</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.218521788397247</v>
+        <v>2.488694961150347</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8028</v>
+        <v>6861</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>581.447614046666</v>
+        <v>641.4917240583482</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.99393633041125</v>
+        <v>50.77216339627185</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.94527333024367</v>
+        <v>25.84697409508722</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7904895318454724</v>
+        <v>0.7024632951146865</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-4.620623667959533</v>
+        <v>-1.394568877050371</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6944</v>
+        <v>8033</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>577.9681485390425</v>
+        <v>620.2782095018508</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1060</v>
+        <v>141</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>68.19452589548648</v>
+        <v>56.66441516214303</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.99932671764638</v>
+        <v>10.05030372839027</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7789729603803098</v>
+        <v>2.610204771900784</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>13.31361913698993</v>
+        <v>1.356757749881036</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8044</v>
+        <v>6957</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>563.4484114182055</v>
+        <v>620.2471825462592</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>29.65</v>
+        <v>187</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.45741482672834</v>
+        <v>59.51098355806415</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.2849873645503</v>
+        <v>27.04718262194713</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4436308756913339</v>
+        <v>0.2704218402409923</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.2099703258275556</v>
+        <v>-0.5347178919340365</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6902</v>
+        <v>7753</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>554.1846830149278</v>
+        <v>608.2216756010567</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>138</v>
+        <v>43.75</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.19954816108441</v>
+        <v>59.39799530516563</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>28.59612986500923</v>
+        <v>17.79366023701437</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6511508553302792</v>
+        <v>6.857273643790124</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.166191946419307</v>
+        <v>0.009020086288440201</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7734</v>
+        <v>6894</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>539.800393267008</v>
+        <v>606.9384912331565</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3390</v>
+        <v>377.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.97043834293486</v>
+        <v>53.94136670173378</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.93445033836064</v>
+        <v>23.58402507518062</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4931487522638342</v>
+        <v>0.7844412841538322</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>29.27862496943636</v>
+        <v>0.8658599954281017</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6859</v>
+        <v>7822</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>536.8121557251402</v>
+        <v>604.3623012407505</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>130</v>
+        <v>1200</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.25293021408339</v>
+        <v>54.27515746664086</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.18253275318658</v>
+        <v>17.21887346573343</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8914014770104827</v>
+        <v>1.090719256876131</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4068213240860139</v>
+        <v>28.57377088343023</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7769</v>
+        <v>7827</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>521.9708577759692</v>
+        <v>594.8866534259499</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6810</v>
+        <v>161</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.00043414292588</v>
+        <v>57.11139727360312</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.56548144747025</v>
+        <v>22.21171365385534</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7044342559665737</v>
+        <v>0.6267340466864252</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-126.1970910329629</v>
+        <v>-0.0548886082310167</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7631</v>
+        <v>6870</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>511.6067827930135</v>
+        <v>591.8964962746046</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>137.5</v>
+        <v>262.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.69313329307521</v>
+        <v>49.8830336480443</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.99058558165039</v>
+        <v>28.80770009358277</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.141717934597029</v>
+        <v>0.4955383435187016</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.648535106885883</v>
+        <v>-6.033176344784074</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6928</v>
+        <v>7704</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>501.8738335223979</v>
+        <v>582.7606145648099</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>49.2</v>
+        <v>63.7</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.1471824693401</v>
+        <v>57.35948116589308</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.40684525873264</v>
+        <v>13.6889562742332</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.011638332486196</v>
+        <v>1.782474175995678</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4998439237105921</v>
+        <v>-0.012154692021827</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6862</v>
+        <v>8028</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>489.4810205302214</v>
+        <v>581.447614046666</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>203.5</v>
+        <v>310</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.51991980843403</v>
+        <v>52.99393631765516</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25.14613327263847</v>
+        <v>39.94527322435439</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.848102053022136</v>
+        <v>0.7904895318454724</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.356374032530837</v>
+        <v>-4.620623666929223</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7402</v>
+        <v>6983</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>485.6921934280942</v>
+        <v>578.9012155201899</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>103</v>
+        <v>381</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>56.46334493457642</v>
+        <v>51.80608198604792</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.47097677334532</v>
+        <v>14.26201678926466</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.674648141193949</v>
+        <v>0.8781915292436479</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.450059123455073</v>
+        <v>4.469579559961279</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7722</v>
+        <v>6971</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>484.7679627630494</v>
+        <v>568.3009305998629</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>306</v>
+        <v>28.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.47606276494113</v>
+        <v>58.30976094084023</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>35.60864650269288</v>
+        <v>21.09794596053411</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5092886283329989</v>
+        <v>0.486963579182307</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4930536015098958</v>
+        <v>0.2240852138310297</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7750</v>
+        <v>6887</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>484.2556689358536</v>
+        <v>566.2364550028225</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2165</v>
+        <v>37</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>45.33070934809402</v>
+        <v>54.12285076825078</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.04083371026343</v>
+        <v>6.24575722075843</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9340618211353198</v>
+        <v>1.980662614387816</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-6.122665174387041</v>
+        <v>0.3383032853189991</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7749</v>
+        <v>7792</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>478.0427255002033</v>
+        <v>563.4521474745658</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.22356017802628</v>
+        <v>51.71156252302769</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.50839608787883</v>
+        <v>20.12595598594388</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3517584814480659</v>
+        <v>0.8146125871356948</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-3.451554680362857</v>
+        <v>3.355353819989612</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6919</v>
+        <v>8044</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>473.0972356639342</v>
+        <v>563.4484114182055</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108</v>
+        <v>29.65</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.17007294771037</v>
+        <v>53.45741486637535</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.17705954851919</v>
+        <v>24.28498743809497</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.934740424771872</v>
+        <v>0.4436308756913339</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>2.488694963875248</v>
+        <v>-0.2099703258790699</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6965</v>
+        <v>7769</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>467.0920970832746</v>
+        <v>542.0186740181224</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>6810</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.45741452168003</v>
+        <v>47.0004341454753</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.69263635366165</v>
+        <v>22.56548139901032</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.393502476622021</v>
+        <v>0.7099958897863208</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0518094424516737</v>
+        <v>-126.1970910329629</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8039</v>
+        <v>6859</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>464.8515190728088</v>
+        <v>536.8121557251401</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>145.5</v>
+        <v>130</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.50214126185991</v>
+        <v>53.25293033458088</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.41499126986798</v>
+        <v>29.18253276401277</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5039449821312487</v>
+        <v>0.8914014770104827</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3313143995788108</v>
+        <v>0.4068213230557225</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6971</v>
+        <v>7631</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>453.3009305998629</v>
+        <v>511.6067827930135</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>28.2</v>
+        <v>137.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.30976089983504</v>
+        <v>54.69313329991625</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.09794590645961</v>
+        <v>11.99058558424105</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.486963579182307</v>
+        <v>1.141717934597029</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2240852138310297</v>
+        <v>2.648535106885883</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8033</v>
+        <v>6928</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>450.2782095018508</v>
+        <v>501.8738335223996</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>141</v>
+        <v>49.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.66441509514306</v>
+        <v>59.1471825897365</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10.0503036844366</v>
+        <v>21.40684524923422</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.610204771900784</v>
+        <v>1.011638332486196</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.356757750313756</v>
+        <v>0.4998439235045333</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7747</v>
+        <v>6862</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>443.7808144940298</v>
+        <v>489.4810205302214</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>126</v>
+        <v>203.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.8073119965563</v>
+        <v>52.51991982032907</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6.319198837462527</v>
+        <v>25.14613321353513</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.500715446910843</v>
+        <v>0.848102053022136</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2799580361935918</v>
+        <v>1.356374032324775</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7704</v>
+        <v>7722</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>442.7606145648099</v>
+        <v>484.7679627630496</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>63.7</v>
+        <v>306</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.35948118685805</v>
+        <v>50.47606279650679</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.68895610604551</v>
+        <v>35.6086465990246</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.782474175995678</v>
+        <v>0.5092886283329989</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0121546916097141</v>
+        <v>0.493053599037184</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6861</v>
+        <v>7750</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>441.4917240583483</v>
+        <v>484.2556689358536</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>358</v>
+        <v>2165</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.77216339304736</v>
+        <v>45.33070933917042</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>25.84697415750328</v>
+        <v>20.04083369671392</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7024632951146865</v>
+        <v>0.9340618211353198</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.394568876988572</v>
+        <v>-6.122665171296088</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7721</v>
+        <v>7749</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>437.6961596582789</v>
+        <v>478.0427255002033</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>73</v>
+        <v>477</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.70268802639004</v>
+        <v>47.22356017802628</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.04913322974626</v>
+        <v>23.50839608787883</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9141247940214212</v>
+        <v>0.3517584814480659</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5350572153940909</v>
+        <v>-3.451554680362857</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6924</v>
+        <v>6965</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>435.429480669023</v>
+        <v>467.0920970832742</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>119.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.1205137599675</v>
+        <v>48.45741462401766</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.99216189522832</v>
+        <v>23.69263635366165</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1212943674061022</v>
+        <v>1.393502476622021</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>1</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-5.347849773914057</v>
+        <v>0.0518094413183437</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6922</v>
+        <v>8039</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>432.069673957493</v>
+        <v>464.8515190728088</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>180</v>
+        <v>145.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.795170070319</v>
+        <v>51.50214125095444</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.41671278194237</v>
+        <v>21.41499117343484</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3329058974201626</v>
+        <v>0.5039449821312487</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.981359554934873</v>
+        <v>0.3313143997024381</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6887</v>
+        <v>7751</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>426.2364550028225</v>
+        <v>450.7110780336453</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>37</v>
+        <v>1475</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.12285078106922</v>
+        <v>43.29846768229011</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6.245757330660361</v>
+        <v>15.67056444323636</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.980662614387816</v>
+        <v>0.6319550966217808</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3383032852983982</v>
+        <v>12.76604403088687</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7792</v>
+        <v>7747</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>423.4521474745658</v>
+        <v>443.7808144940298</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>283</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.71156249263301</v>
+        <v>50.80731200022533</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.12595597908563</v>
+        <v>6.319198854189588</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8146125871356948</v>
+        <v>1.500715446910843</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>3.355353819989612</v>
+        <v>-0.2799580360905693</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6997</v>
+        <v>6865</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>416.8937455086792</v>
+        <v>438.8344858319791</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>26.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.84201835977056</v>
+        <v>49.48041580900015</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8.712851090007337</v>
+        <v>20.07219009260236</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2499707546530886</v>
+        <v>0.831712961211588</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.8256333606093231</v>
+        <v>0.6463804561760367</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6983</v>
+        <v>6924</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>408.90121552019</v>
+        <v>435.429480669023</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>381</v>
+        <v>119.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.80608201304513</v>
+        <v>42.1205137599675</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.26201679569353</v>
+        <v>31.99216189522832</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8781915292436479</v>
+        <v>0.1212943674061022</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>1</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>4.469579559137019</v>
+        <v>-5.347849773914057</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6951</v>
+        <v>6922</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>408.7087148174514</v>
+        <v>432.069673957493</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>77.7</v>
+        <v>180</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>36.7741380115889</v>
+        <v>44.79517019107259</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.66231887467358</v>
+        <v>19.41671272375752</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8628186506454721</v>
+        <v>0.3329058974201626</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.482349329560485</v>
+        <v>-1.981359556377302</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7728</v>
+        <v>6918</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>403.0607217379679</v>
+        <v>424.0672965846733</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>715</v>
+        <v>73.2</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.27478885350898</v>
+        <v>46.12053879170895</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>11.35985058849589</v>
+        <v>6.438174308258999</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2919676931122593</v>
+        <v>0.4121698294260922</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.6469522613199361</v>
+        <v>0.07188274569835849</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7786</v>
+        <v>7721</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>399.4327098691248</v>
+        <v>422.6961596582789</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>126.5</v>
+        <v>73</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.56033112730417</v>
+        <v>44.70268800668272</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.3019238648667</v>
+        <v>16.0491332647495</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4690312431532978</v>
+        <v>0.9141247940214212</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.101915617988101</v>
+        <v>-0.5350572152704454</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6906</v>
+        <v>6997</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>384.5802122588451</v>
+        <v>416.8937455086792</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>88</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.61134921060811</v>
+        <v>51.8420183696116</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>26.49091618545692</v>
+        <v>8.712850983415375</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4162605353150401</v>
+        <v>0.2499707546530886</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.094908707648927</v>
+        <v>0.8256333607123452</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7714</v>
+        <v>6951</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>375.6336957515318</v>
+        <v>408.7087148174514</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>129.5</v>
+        <v>77.7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.24056825947224</v>
+        <v>36.77413813158631</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.08897159955938</v>
+        <v>25.66231880154454</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2812254931217651</v>
+        <v>0.8628186506454721</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>1</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0656790902083859</v>
+        <v>-0.4823493295192743</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7768</v>
+        <v>7728</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>366.0517061562181</v>
+        <v>403.0607217379679</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>360.5</v>
+        <v>715</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>40.19707048410588</v>
+        <v>47.27478889616646</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.73985381225555</v>
+        <v>11.35985058179878</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7772778547311792</v>
+        <v>0.2919676931122593</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.839530993451687</v>
+        <v>-0.6469522629683846</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7839</v>
+        <v>7786</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>364.302722972685</v>
+        <v>399.4327098691234</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>43</v>
+        <v>126.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.05975568771642</v>
+        <v>51.56033122978712</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6.684772237176746</v>
+        <v>21.30192395899229</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.330272297268505</v>
+        <v>0.4690312431532978</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.090208158163065</v>
+        <v>1.101915619842622</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7822</v>
+        <v>7730</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>359.3623012407506</v>
+        <v>393.6941010143353</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1200</v>
+        <v>185.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.27515746899637</v>
+        <v>48.95554584582669</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.21887348471154</v>
+        <v>16.30972648952818</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.090719256876131</v>
+        <v>1.041820069091911</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>28.57377088343023</v>
+        <v>-1.430733609040381</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6877</v>
+        <v>6906</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>349.5514728059325</v>
+        <v>384.5802122588451</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>34.14920984619228</v>
+        <v>48.61134924742085</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.00436739766188</v>
+        <v>26.49091611725878</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3240989174760682</v>
+        <v>0.4162605353150401</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.784920437541363</v>
+        <v>-2.094908707648927</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7760</v>
+        <v>7714</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>349.4572523456977</v>
+        <v>375.6336957515318</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>32.7</v>
+        <v>129.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.75630035612453</v>
+        <v>51.24056825947224</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46.1443881888267</v>
+        <v>23.08897166562422</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.011207492162544</v>
+        <v>0.2812254931217651</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.303635721859244</v>
+        <v>0.0656790902083859</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7805</v>
+        <v>7768</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>347.6511018402334</v>
+        <v>366.0517061562181</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>678</v>
+        <v>360.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.63244746882586</v>
+        <v>40.19707048087652</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.7366443186708</v>
+        <v>16.73985371301482</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7483519291627418</v>
+        <v>0.7772778547311792</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-8.740597477384883</v>
+        <v>-2.839530991391091</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7772</v>
+        <v>7839</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>340.1294780696025</v>
+        <v>364.302722972685</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.67423205421835</v>
+        <v>42.05975568771642</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.203611071635001</v>
+        <v>6.684772237176746</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4245096535505871</v>
+        <v>1.330272297268505</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.4839357036050984</v>
+        <v>-2.090208158163065</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6933</v>
+        <v>6952</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>335.7059670329188</v>
+        <v>362.9597683142277</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>152.5</v>
+        <v>35.85</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.01527108678904</v>
+        <v>37.91174062473008</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.92364504974856</v>
+        <v>20.82022078674963</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4576024383537254</v>
+        <v>0.8297540632186148</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.8477344885725797</v>
+        <v>0.0518900041116028</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6899</v>
+        <v>6863</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>333.3204522194035</v>
+        <v>357.5025604167544</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>59</v>
+        <v>93.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.82417047374615</v>
+        <v>34.90732383117142</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.2896101344054</v>
+        <v>22.77598689612634</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2988669414679604</v>
+        <v>0.9177096365706572</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6272655450776023</v>
+        <v>-1.049697996157431</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6895</v>
+        <v>6921</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>325.5265376816398</v>
+        <v>353.2280794607738</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.59456899378898</v>
+        <v>38.17882322842236</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.41396862470454</v>
+        <v>26.71281750198446</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.144045160950634</v>
+        <v>1.430716838069185</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2064781654447484</v>
+        <v>0.1902567867348548</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6865</v>
+        <v>6877</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>323.8344858319792</v>
+        <v>349.5514728059325</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>26.8</v>
+        <v>127</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>49.48041585347485</v>
+        <v>34.14920992576116</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.07219009260236</v>
+        <v>22.00436749852741</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.831712961211588</v>
+        <v>0.3240989174760682</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.6463804560730075</v>
+        <v>-1.784920438159547</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6855</v>
+        <v>7760</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>318.6022029429706</v>
+        <v>349.4572523456977</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>118</v>
+        <v>32.7</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.51869724397727</v>
+        <v>46.75630019125195</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.63634601221199</v>
+        <v>46.14438810779466</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3288629448632422</v>
+        <v>1.011207492162544</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-3.849441322346269</v>
+        <v>0.3036357221168152</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7780</v>
+        <v>7805</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>318.5307662890571</v>
+        <v>347.6511018402334</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18.2</v>
+        <v>678</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.8507798198803</v>
+        <v>35.63244760643788</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.32382208704134</v>
+        <v>26.73664431493495</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8171854884342763</v>
+        <v>0.7483519291627418</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1167066596664139</v>
+        <v>-8.740597477384883</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7736</v>
+        <v>7772</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>315.151587424634</v>
+        <v>340.1294780696025</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>140</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.28680392072309</v>
+        <v>42.67423205421835</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.97139351736754</v>
+        <v>9.203611071635001</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5059354554443779</v>
+        <v>0.4245096535505871</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.182604626808708</v>
+        <v>-0.4839357036050984</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6918</v>
+        <v>6933</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>314.0672965846733</v>
+        <v>335.7059670329188</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>73.2</v>
+        <v>152.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.12053879170895</v>
+        <v>43.01527116720145</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6.438174237642949</v>
+        <v>17.92364505957421</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4121698294260922</v>
+        <v>0.4576024383537254</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0718827455953258</v>
+        <v>-0.8477344892937762</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6903</v>
+        <v>6899</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>311.9557139674922</v>
+        <v>333.3204522194035</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>381</v>
+        <v>59</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.50950099962427</v>
+        <v>43.82417042970139</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.73583504510684</v>
+        <v>19.28961005771894</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4885112552888046</v>
+        <v>0.2988669414679604</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.347677796044892</v>
+        <v>-0.6272655449127469</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7751</v>
+        <v>6895</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>310.7110780336452</v>
+        <v>325.5265376816399</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1475</v>
+        <v>155</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.29846766883514</v>
+        <v>44.59456903822905</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.67056448722409</v>
+        <v>20.4139686661066</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6319550966217808</v>
+        <v>1.144045160950634</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>12.76604402954769</v>
+        <v>0.2064781647235138</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7717</v>
+        <v>6855</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>307.0340304804653</v>
+        <v>318.6022029429706</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>497.5</v>
+        <v>118</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>32.50465389561982</v>
+        <v>51.51869799808902</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.89618306607867</v>
+        <v>16.63634730346106</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9713507687300074</v>
+        <v>0.3288629448632422</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-7.631259675946104</v>
+        <v>-3.849441350679245</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7711</v>
+        <v>7780</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>301.971790026177</v>
+        <v>318.5307662890571</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>340</v>
+        <v>18.2</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.1351718629725</v>
+        <v>43.85077912291329</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.12420681443727</v>
+        <v>18.32382225208202</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8386599540023403</v>
+        <v>0.8171854884342763</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-4.065643738749088</v>
+        <v>0.1167066599933983</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8038</v>
+        <v>7736</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>299.2853544305458</v>
+        <v>315.151587424634</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>40.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.41754314868267</v>
+        <v>47.28680409603079</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.324977003303846</v>
+        <v>15.97139352167743</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.815680244887665</v>
+        <v>0.5059354554443779</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0128459928464797</v>
+        <v>0.1826046258814431</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6923</v>
+        <v>6903</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>296.4557243403337</v>
+        <v>311.9557139674922</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>78.2</v>
+        <v>381</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.97622222943126</v>
+        <v>46.50950101606704</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.44652086838189</v>
+        <v>13.73583504510683</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7628615162957172</v>
+        <v>0.4885112552888046</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.09305571819513631</v>
+        <v>-1.347677796457023</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7744</v>
+        <v>7717</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>296.3518129701966</v>
+        <v>307.0340304804653</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>454</v>
+        <v>497.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.54179404014583</v>
+        <v>32.50465389561982</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.63486665920495</v>
+        <v>12.89618306607867</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6635805325788395</v>
+        <v>0.9713507687300074</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.8168258455596629</v>
+        <v>-7.631259675946104</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7820</v>
+        <v>7711</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>290.9887864523873</v>
+        <v>301.971790026177</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>115</v>
+        <v>340</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.6263097858247</v>
+        <v>39.13517186594846</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>30.19000743852852</v>
+        <v>15.12420683017255</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.972660886707714</v>
+        <v>0.8386599540023403</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.9503389537457484</v>
+        <v>-4.065643736482481</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6910</v>
+        <v>6873</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>290.4616781738188</v>
+        <v>300.5786842518782</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>27.85</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.53825205138119</v>
+        <v>40.54062462980099</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.75833896589578</v>
+        <v>14.0629728209369</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.2692788039881739</v>
+        <v>0.4877853957848211</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0751438607288555</v>
+        <v>-0.7873416903522426</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6967</v>
+        <v>8038</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>286.6064662723102</v>
+        <v>299.2853544305458</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>70.8</v>
+        <v>40.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.4266574516004</v>
+        <v>44.41754323900157</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.654585627171532</v>
+        <v>7.324977003303843</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.173798388720383</v>
+        <v>0.815680244887665</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2740346413101499</v>
+        <v>-0.0128459928876851</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6913</v>
+        <v>6958</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>281.4368386390648</v>
+        <v>299.1873683575082</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>123</v>
+        <v>17.25</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.57278637051117</v>
+        <v>48.94990770105747</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.0622089949202</v>
+        <v>17.92025380136096</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4875016673466108</v>
+        <v>0.6458579275390017</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.162270244593728</v>
+        <v>0.0813816709891836</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6925</v>
+        <v>6923</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>281.3060293709275</v>
+        <v>296.4557243403338</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>62.6</v>
+        <v>78.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.69996169650828</v>
+        <v>46.97622230665561</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.70050218162057</v>
+        <v>12.44652085446805</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.1676273226201875</v>
+        <v>0.7628615162957172</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.6665103182598278</v>
+        <v>0.09305571805089941</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6914</v>
+        <v>7744</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>279.8924814374572</v>
+        <v>296.3518129701966</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>143</v>
+        <v>454</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.24233481600045</v>
+        <v>39.54179404254453</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.47110591136212</v>
+        <v>12.63486663956984</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3192936449469509</v>
+        <v>0.6635805325788395</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.3797780941498968</v>
+        <v>-0.8168258447353729</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7705</v>
+        <v>7740</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>279.1388207808004</v>
+        <v>295.9969568944131</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>31.85</v>
+        <v>155.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.28749460171969</v>
+        <v>38.87286341146303</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.51034674162333</v>
+        <v>14.22028886191591</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3472330329173617</v>
+        <v>0.3310514597106361</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1286460537936609</v>
+        <v>-1.514760239668353</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6937</v>
+        <v>7820</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>278.6915878903224</v>
+        <v>290.9887864523873</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>277</v>
+        <v>115</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.00601573047118</v>
+        <v>33.62630982440274</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.76825288024627</v>
+        <v>30.19000747709336</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5194991726709235</v>
+        <v>0.972660886707714</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.4748353625276289</v>
+        <v>0.9503389535190968</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8047</v>
+        <v>6910</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>277.302970581288</v>
+        <v>290.4616781738188</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>47.8</v>
+        <v>27.85</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.89123522688092</v>
+        <v>43.53825206811094</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6.61756998426641</v>
+        <v>12.75833898147533</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1003241751943108</v>
+        <v>0.2692788039881739</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0568322129332342</v>
+        <v>-0.075143860564005</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6994</v>
+        <v>6967</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>274.3503796934199</v>
+        <v>286.6064662723102</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>51.3</v>
+        <v>70.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>30.93863390431264</v>
+        <v>47.42665752084768</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.54771395136661</v>
+        <v>9.654585636199943</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.226575995089944</v>
+        <v>1.173798388720383</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.676874314137174</v>
+        <v>0.2740346410422623</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7842</v>
+        <v>6913</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>263.7418745789875</v>
+        <v>281.4368386390646</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>123</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>32.38787627193011</v>
+        <v>41.57278644006917</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.55403732284784</v>
+        <v>16.06220899492019</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4627853019242133</v>
+        <v>0.4875016673466108</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.519840414028355</v>
+        <v>-1.162270245108874</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7703</v>
+        <v>6925</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>263.4332873046293</v>
+        <v>281.3060293709275</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>203</v>
+        <v>62.6</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.43284384306064</v>
+        <v>44.69996175624044</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.10277485507888</v>
+        <v>19.70050218077512</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.822801776498347</v>
+        <v>0.1676273226201875</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>1.215931960116439</v>
+        <v>-0.6665103185689214</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6952</v>
+        <v>7818</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>252.9597683142277</v>
+        <v>280.1746961273089</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>35.85</v>
+        <v>63.9</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.91174064161</v>
+        <v>34.16681030379708</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.82022077726655</v>
+        <v>49.569474666681</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8297540632186148</v>
+        <v>1.330192812128201</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0518900040909985</v>
+        <v>1.452671592646655</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6931</v>
+        <v>6914</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>251.4161362448886</v>
+        <v>279.8924814374572</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>40.1</v>
+        <v>143</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.10512186697804</v>
+        <v>51.2423345093756</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>22.87757018916969</v>
+        <v>13.47110596092794</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9310533255802828</v>
+        <v>0.3192936449469509</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.204272900518085</v>
+        <v>0.3797780951802088</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6955</v>
+        <v>7705</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>249.5169035004229</v>
+        <v>279.1388207808002</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>126.5</v>
+        <v>31.85</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.08605730556172</v>
+        <v>51.28749438250217</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>5.922786073219664</v>
+        <v>16.51034700085247</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.238082544063225</v>
+        <v>0.3472330329173617</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.321603181925176</v>
+        <v>0.1286460539997191</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6936</v>
+        <v>6937</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>248.4055501876153</v>
+        <v>278.6915878903224</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>32.6</v>
+        <v>277</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>37.34265756505848</v>
+        <v>45.00601576951258</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.02645693097096</v>
+        <v>12.7682529007328</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6074052592794164</v>
+        <v>0.5194991726709235</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0437978854298933</v>
+        <v>-0.4748353634549014</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6863</v>
+        <v>8047</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>247.5025604167544</v>
+        <v>277.302970581288</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>93.5</v>
+        <v>47.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.90732364853181</v>
+        <v>47.89123526509169</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.77598689612634</v>
+        <v>6.617569967731702</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9177096365706572</v>
+        <v>0.1003241751943108</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.049697995436213</v>
+        <v>0.0568322129126265</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7738</v>
+        <v>6994</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>244.6967712257732</v>
+        <v>274.3503796934199</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>169.5</v>
+        <v>51.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.60314884707996</v>
+        <v>30.93863445977316</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24.35944683719621</v>
+        <v>19.54771410415714</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5851647111185649</v>
+        <v>1.226575995089944</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.595955931132885</v>
+        <v>-0.676874314137174</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6921</v>
+        <v>6931</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>243.2280794607738</v>
+        <v>271.4161362448887</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>70</v>
+        <v>40.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.17882322842236</v>
+        <v>35.10512196277037</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26.71281750198446</v>
+        <v>22.87757017776006</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.430716838069185</v>
+        <v>0.9310533255802828</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1902567867348548</v>
+        <v>0.2042729006623251</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7765</v>
+        <v>6936</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>240.2479035981169</v>
+        <v>268.4055501876155</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>227.5</v>
+        <v>32.6</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.66524734571737</v>
+        <v>37.34265724561708</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26.69345707478684</v>
+        <v>11.026457048753</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.9247903598116824</v>
+        <v>0.6074052592794164</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-3.114810125282447</v>
+        <v>-0.0437978852444412</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6854</v>
+        <v>7842</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>240.0909672681784</v>
+        <v>263.7418745789875</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>128</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.98477839685954</v>
+        <v>32.38787627193011</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.69341935639603</v>
+        <v>26.55403732284784</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4982474863006671</v>
+        <v>0.4627853019242133</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.5687378707237496</v>
+        <v>0.519840414028355</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7823</v>
+        <v>7703</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>240.0573565200355</v>
+        <v>263.4332873046293</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>80.3</v>
+        <v>203</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>26.42627499797625</v>
+        <v>47.43284392826609</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>31.20395791116651</v>
+        <v>12.10277481935195</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5907643254668153</v>
+        <v>0.822801776498347</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.393715224690957</v>
+        <v>1.21593195918917</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7803</v>
+        <v>7823</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>238.3460896856574</v>
+        <v>260.0573565200355</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>22.5</v>
+        <v>80.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.69642491265894</v>
+        <v>26.42627499797625</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>20.50977792245749</v>
+        <v>31.20395791116651</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6693970703709772</v>
+        <v>0.5907643254668153</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2554812741174705</v>
+        <v>-1.393715224690957</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6969</v>
+        <v>6955</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>232.1079980017499</v>
+        <v>249.5169035004229</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.6</v>
+        <v>126.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>22.17193342179605</v>
+        <v>44.08605726122924</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.67697166167157</v>
+        <v>5.922786060593928</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8632164535627843</v>
+        <v>1.238082544063225</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1213129917494967</v>
+        <v>-1.321603181100948</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6885</v>
+        <v>7738</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>227.2989966044771</v>
+        <v>244.6967712257732</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>21.35</v>
+        <v>169.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.67096060302111</v>
+        <v>46.60314902054248</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>21.11067455547635</v>
+        <v>24.35944683888939</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5289356100154993</v>
+        <v>0.5851647111185649</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2811134209699795</v>
+        <v>0.5959559310298388</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7740</v>
+        <v>7765</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>220.996956894413</v>
+        <v>240.2479035981169</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>155.5</v>
+        <v>227.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.87286359211138</v>
+        <v>36.66524736132646</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.22028885451648</v>
+        <v>26.69345707478684</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3310514597106361</v>
+        <v>0.9247903598116824</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-1.514760242656196</v>
+        <v>-3.114810126209696</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6869</v>
+        <v>6854</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>215.8989108482114</v>
+        <v>240.0909672681784</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>36.08755126720683</v>
+        <v>36.9847784634844</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.04531409432174</v>
+        <v>17.6934193577942</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.768752918730768</v>
+        <v>0.4982474863006671</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.5009296802639833</v>
+        <v>-0.5687378719601144</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6908</v>
+        <v>7803</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>215.2216068748661</v>
+        <v>238.3460896856574</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>38.9</v>
+        <v>22.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.54444672861931</v>
+        <v>36.69642473355921</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.87647763657589</v>
+        <v>20.50977808901189</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.593231008660147</v>
+        <v>0.6693970703709772</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.07055050317722129</v>
+        <v>0.2554812742823165</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7810</v>
+        <v>6969</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>207.7770381113316</v>
+        <v>232.1079980017497</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>205</v>
+        <v>25.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.8549507578528</v>
+        <v>22.17193326141044</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.97071885932683</v>
+        <v>20.67697167299044</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5320695624019327</v>
+        <v>0.8632164535627843</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.7511032428862201</v>
+        <v>-0.121312991543443</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6934</v>
+        <v>6885</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>207.5923458506415</v>
+        <v>227.2989966044771</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>67.2</v>
+        <v>21.35</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.13009147074494</v>
+        <v>39.67096064537615</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>29.92280432383121</v>
+        <v>21.11067452391608</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4107984303507546</v>
+        <v>0.5289356100154993</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0153282447578595</v>
+        <v>-0.2811134210317969</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7730</v>
+        <v>6869</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>203.6941010143353</v>
+        <v>215.8989108482113</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>185.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.9555458520288</v>
+        <v>36.08755165775783</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.30972646171928</v>
+        <v>17.04531488533251</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.041820069091911</v>
+        <v>0.768752918730768</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-1.430733609267038</v>
+        <v>-0.5009296788215671</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7732</v>
+        <v>6908</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>201.7412671531215</v>
+        <v>215.2216068748661</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>35.7</v>
+        <v>38.9</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.68741430154793</v>
+        <v>46.54444683163501</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.48074072057244</v>
+        <v>10.87647771223247</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5297129749078693</v>
+        <v>1.593231008660147</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1618856744832982</v>
+        <v>0.07055050307419131</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6873</v>
+        <v>7810</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>190.5786842518771</v>
+        <v>207.7770381113316</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>205</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.54062452158468</v>
+        <v>40.8549507578528</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.06297254879478</v>
+        <v>14.97071887766736</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4877853957848211</v>
+        <v>0.5320695624019327</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.7873416909704305</v>
+        <v>-0.7511032428862201</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6958</v>
+        <v>6934</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>189.1873683575082</v>
+        <v>207.5923458506415</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.25</v>
+        <v>67.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>48.9499076899267</v>
+        <v>37.13009133421094</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.92025381963597</v>
+        <v>29.92280431525399</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6458579275390017</v>
+        <v>0.4107984303507546</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0813816709788812</v>
+        <v>0.0153282453348175</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7791</v>
+        <v>7732</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>167.4061172467397</v>
+        <v>201.7412671531214</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>61.9</v>
+        <v>35.7</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>34.86399749550144</v>
+        <v>51.68741430698494</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.09737996180882</v>
+        <v>15.48074072057244</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8459428510173201</v>
+        <v>0.5297129749078693</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.3873565333138968</v>
+        <v>-0.1618856745966328</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7821</v>
+        <v>7791</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>166.8865372568107</v>
+        <v>167.4061172467397</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>43.25</v>
+        <v>61.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>38.75237128606881</v>
+        <v>34.86399753188743</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.83232401477857</v>
+        <v>20.09737998568233</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5950244760449518</v>
+        <v>0.8459428510173201</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.1528665064833312</v>
+        <v>-0.3873565333551139</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7818</v>
+        <v>7821</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>165.1746961273089</v>
+        <v>166.8865372568107</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>63.9</v>
+        <v>43.25</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>34.16681050509521</v>
+        <v>38.75237153162946</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>49.56947433987869</v>
+        <v>16.83232401434537</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.330192812128201</v>
+        <v>0.5950244760449518</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,11 +6877,11 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1.452671591307276</v>
+        <v>0.1528665063287917</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>49.9355244178523</v>
+        <v>49.93552452306798</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6.905250456489331</v>
+        <v>6.90525046516558</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.8878966389991048</v>
@@ -6968,7 +6968,7 @@
         <v>33.94024280797561</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.07008946562749</v>
+        <v>18.07008948341471</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.737118338599362</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.50907129903079</v>
+        <v>39.50907124115874</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.33662451627898</v>
+        <v>14.33662455908488</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.2822097765665299</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1440231125228033</v>
+        <v>0.1440231125846263</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.51594525920108</v>
+        <v>46.51594532790789</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.52065515874054</v>
+        <v>17.52065516720439</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.3926446947375894</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.6323115666055674</v>
+        <v>0.6323115665025503</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>40.12280509979368</v>
+        <v>40.12280528029212</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.95417330325656</v>
+        <v>11.95417330959791</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.4268598365974212</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0328490757262045</v>
+        <v>-0.0328490763237678</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>38.47280138982749</v>
+        <v>38.47280149548808</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.17234348006493</v>
+        <v>17.17234357321129</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.884267280823485</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0612273806632081</v>
+        <v>-0.0612273807250257</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.66428468960834</v>
+        <v>39.66428481233908</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15.48765871678197</v>
+        <v>15.48765873320208</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.6950447522727886</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0175705432709184</v>
+        <v>-0.0175705433327365</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
